--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_3.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_3.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_24</t>
+          <t>model_14_3_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.997364155565733</v>
+        <v>0.9994534625866291</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7032369569492729</v>
+        <v>0.7082266831686346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9388646699381096</v>
+        <v>0.9992843909562557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9969089003322787</v>
+        <v>0.9996217787156437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9963476437192493</v>
+        <v>0.999541154180653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001564751118731728</v>
+        <v>0.0003244482177638957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1761713618508709</v>
+        <v>0.1732092448221083</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001247007011796847</v>
+        <v>0.0002521618733626926</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002549430287127273</v>
+        <v>0.0002504870456295285</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00189821864946206</v>
+        <v>0.0002513249336741718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01397697702749638</v>
+        <v>0.01081443054398766</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03955693515341814</v>
+        <v>0.01801244619045108</v>
       </c>
       <c r="N2" t="n">
-        <v>1.00234297283046</v>
+        <v>1.000485811034107</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04124095577704344</v>
+        <v>0.01877927331568248</v>
       </c>
       <c r="P2" t="n">
-        <v>114.9200569944019</v>
+        <v>118.0667692200232</v>
       </c>
       <c r="Q2" t="n">
-        <v>177.0827240626801</v>
+        <v>180.2294362883014</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_23</t>
+          <t>model_14_3_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9972382368217361</v>
+        <v>0.9995079564481507</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7032001618584317</v>
+        <v>0.7075416498855512</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9416870732359938</v>
+        <v>0.9993610191784879</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970537143428668</v>
+        <v>0.9996623025769892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9965179359434048</v>
+        <v>0.9995903028880765</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001639501924574832</v>
+        <v>0.0002920983075524203</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1761932050062593</v>
+        <v>0.1736159101708435</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001189437081299749</v>
+        <v>0.000225160096010325</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002429992784529457</v>
+        <v>0.0002236490470139528</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001809713626703497</v>
+        <v>0.0002244045715121389</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0142764451696979</v>
+        <v>0.01025558989705738</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04049076344766584</v>
+        <v>0.01709088375574594</v>
       </c>
       <c r="N3" t="n">
-        <v>1.002454900602901</v>
+        <v>1.000437372046088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04221453907506831</v>
+        <v>0.01781847806023471</v>
       </c>
       <c r="P3" t="n">
-        <v>114.8267255756023</v>
+        <v>118.2768402853129</v>
       </c>
       <c r="Q3" t="n">
-        <v>176.9893926438805</v>
+        <v>180.4395073535911</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_22</t>
+          <t>model_14_3_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9970927741134804</v>
+        <v>0.9995570076732483</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7031525906592557</v>
+        <v>0.7068659849098258</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9445258370752583</v>
+        <v>0.9994290823616344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9971940996663334</v>
+        <v>0.999698633272584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9966850246745924</v>
+        <v>0.9996341606234217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001725854871857167</v>
+        <v>0.0002629793814319526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.176221445325059</v>
+        <v>0.1740170140876414</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001131533436896186</v>
+        <v>0.0002011764139715165</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002314207907305488</v>
+        <v>0.0001995880832829048</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001722873537381753</v>
+        <v>0.0002003822486272107</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01459286767279687</v>
+        <v>0.009722745751311329</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04154340948763315</v>
+        <v>0.01621663903008119</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002584200788017</v>
+        <v>1.000393770957113</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04331199843623473</v>
+        <v>0.01690701492666234</v>
       </c>
       <c r="P4" t="n">
-        <v>114.7240655467375</v>
+        <v>118.4868698529138</v>
       </c>
       <c r="Q4" t="n">
-        <v>176.8867326150158</v>
+        <v>180.649536921192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_21</t>
+          <t>model_14_3_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9969253580711805</v>
+        <v>0.9996010821046799</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7030930469650822</v>
+        <v>0.7062023273974593</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9473700476004417</v>
+        <v>0.9994890600324117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9973286555473135</v>
+        <v>0.999731065325966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9968476030374435</v>
+        <v>0.9996730615450213</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001825240266562849</v>
+        <v>0.0002368148950178096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.176256793034074</v>
+        <v>0.1744109898554939</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001073518693795271</v>
+        <v>0.0001800418545981508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002203230949213885</v>
+        <v>0.0001781090984363211</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001638377596503934</v>
+        <v>0.0001790749355197358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01492731374608331</v>
+        <v>0.009214712271188587</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04272283074145308</v>
+        <v>0.01538879121366618</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00273301504784</v>
+        <v>1.000354593684729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04454163009456835</v>
+        <v>0.01604392391482132</v>
       </c>
       <c r="P5" t="n">
-        <v>114.612087295404</v>
+        <v>118.69646351135</v>
       </c>
       <c r="Q5" t="n">
-        <v>176.7747543636823</v>
+        <v>180.8591305796282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_20</t>
+          <t>model_14_3_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9967334072697206</v>
+        <v>0.9996406130782197</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7030199413007813</v>
+        <v>0.7055530465253701</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9502139955383071</v>
+        <v>0.9995414080469108</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9974558894896098</v>
+        <v>0.9997598466262908</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9970043717209011</v>
+        <v>0.9997072981627046</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001939190554152357</v>
+        <v>0.0002133476014754164</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1763001917144034</v>
+        <v>0.1747964310286393</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001015509306815385</v>
+        <v>0.0001615957861501499</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002098292868624605</v>
+        <v>0.0001590479213267006</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001556901087719995</v>
+        <v>0.0001603224149437608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01528074884676565</v>
+        <v>0.008730600712331237</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04403624137176512</v>
+        <v>0.01460642329509235</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002903637982471</v>
+        <v>1.000319455041582</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04591095533454759</v>
+        <v>0.01522824897422894</v>
       </c>
       <c r="P6" t="n">
-        <v>114.4909692662069</v>
+        <v>118.9051755811983</v>
       </c>
       <c r="Q6" t="n">
-        <v>176.6536363344851</v>
+        <v>181.0678426494765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_19</t>
+          <t>model_14_3_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9965140498591637</v>
+        <v>0.9996760127832761</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7029311307313888</v>
+        <v>0.7049201920480064</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9530504775438301</v>
+        <v>0.9995866447824455</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9975739476421841</v>
+        <v>0.9997852436452834</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9971537079026401</v>
+        <v>0.9997372032037283</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002069410588805688</v>
+        <v>0.0001923328073663468</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1763529135048115</v>
+        <v>0.1751721207842924</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009576522060826007</v>
+        <v>0.0001456555460470213</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002000922656671254</v>
+        <v>0.000142228074008749</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001479287431376927</v>
+        <v>0.0001439424412469999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01565426929951056</v>
+        <v>0.008269125264786953</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04549077476594224</v>
+        <v>0.01386841041238493</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00309862234741</v>
+        <v>1.000287988637088</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04742741122661404</v>
+        <v>0.01445881735520739</v>
       </c>
       <c r="P7" t="n">
-        <v>114.3609829039166</v>
+        <v>119.1125666295835</v>
       </c>
       <c r="Q7" t="n">
-        <v>176.5236499721948</v>
+        <v>181.2752336978617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_18</t>
+          <t>model_14_3_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9962640797349062</v>
+        <v>0.9997076356122472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7028248549645529</v>
+        <v>0.704305568178041</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9558723862697429</v>
+        <v>0.9996252655580188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9976808226655655</v>
+        <v>0.9998075104102363</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9972938803881745</v>
+        <v>0.9997630889661467</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00221780365271205</v>
+        <v>0.0001735601300540443</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1764160033908794</v>
+        <v>0.1755369880638725</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009000923636101457</v>
+        <v>0.000132046596852782</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001912775896348005</v>
+        <v>0.0001274813201917494</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001406436371477584</v>
+        <v>0.0001297639585222657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01604900618231935</v>
+        <v>0.007829542273345489</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04709356275237678</v>
+        <v>0.01317422218022925</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003320818013417</v>
+        <v>1.00025987945578</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04909843321585963</v>
+        <v>0.0137350760928411</v>
       </c>
       <c r="P8" t="n">
-        <v>114.2224758368971</v>
+        <v>119.317972895405</v>
       </c>
       <c r="Q8" t="n">
-        <v>176.3851429051754</v>
+        <v>181.4806399636832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_17</t>
+          <t>model_14_3_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9959799091927908</v>
+        <v>0.9997358369727372</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7026985786379434</v>
+        <v>0.7037101600536724</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9586676100362349</v>
+        <v>0.9996578254145996</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9977742671046683</v>
+        <v>0.9998268756892207</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9974228811702208</v>
+        <v>0.9997852709836624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002386499562039995</v>
+        <v>0.0001568185842318127</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1764909664732081</v>
+        <v>0.1758904480467895</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000843076827211995</v>
+        <v>0.000120573356675599</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001835706209562982</v>
+        <v>0.0001146561521717719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001339391518387488</v>
+        <v>0.0001176141385918244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0164965123366095</v>
+        <v>0.007465772183015505</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04885181226976124</v>
+        <v>0.01252272271639888</v>
       </c>
       <c r="N9" t="n">
-        <v>1.003573414050853</v>
+        <v>1.000234811579789</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05093153505527741</v>
+        <v>0.01305584094804567</v>
       </c>
       <c r="P9" t="n">
-        <v>114.0758552100679</v>
+        <v>119.5208418703691</v>
       </c>
       <c r="Q9" t="n">
-        <v>176.2385222783462</v>
+        <v>181.6835089386474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_16</t>
+          <t>model_14_3_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9956575956213363</v>
+        <v>0.9997609202448526</v>
       </c>
       <c r="C10" t="n">
-        <v>0.702549862109306</v>
+        <v>0.7031348209008847</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9614306754913284</v>
+        <v>0.9996847433995039</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9978516899775491</v>
+        <v>0.9998435772335166</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9975385340546084</v>
+        <v>0.9998040255641545</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002577838821276736</v>
+        <v>0.0001419280703631189</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1765792510288268</v>
+        <v>0.1762319942212415</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007867172395060452</v>
+        <v>0.0001110881642231573</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001771850547094393</v>
+        <v>0.0001035951128776956</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001279283893300219</v>
+        <v>0.0001073416385504264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01708507296510882</v>
+        <v>0.007122197721033654</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05077242185750781</v>
+        <v>0.01191335680499493</v>
       </c>
       <c r="N10" t="n">
-        <v>1.003859915003257</v>
+        <v>1.000212515337909</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05293390896938428</v>
+        <v>0.01242053306823191</v>
       </c>
       <c r="P10" t="n">
-        <v>113.9216077945176</v>
+        <v>119.7203803508795</v>
       </c>
       <c r="Q10" t="n">
-        <v>176.0842748627958</v>
+        <v>181.8830474191577</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_15</t>
+          <t>model_14_3_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9952927993105725</v>
+        <v>0.9997831876899548</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7023755925155527</v>
+        <v>0.7025799524511614</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9641502331607683</v>
+        <v>0.9997065940898868</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9979102648418556</v>
+        <v>0.9998578465393732</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9976383779600231</v>
+        <v>0.9998196808561235</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002794397669726169</v>
+        <v>0.000128709153046946</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1766827049877333</v>
+        <v>0.1765613881020663</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007312451012294674</v>
+        <v>0.0001033885535636802</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001723540059183976</v>
+        <v>9.414488779772304e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001227392580206722</v>
+        <v>9.876672068070161e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01770587466159609</v>
+        <v>0.006794927439712254</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05286206266999207</v>
+        <v>0.01134500564331927</v>
       </c>
       <c r="N11" t="n">
-        <v>1.004184178390602</v>
+        <v>1.000192722053374</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05511251011740881</v>
+        <v>0.01182798602095462</v>
       </c>
       <c r="P11" t="n">
-        <v>113.7602773967609</v>
+        <v>119.9159106532903</v>
       </c>
       <c r="Q11" t="n">
-        <v>175.9229444650392</v>
+        <v>182.0785777215686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_14</t>
+          <t>model_14_3_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9948806506847542</v>
+        <v>0.9998029001791018</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7021725812884244</v>
+        <v>0.7020460208537187</v>
       </c>
       <c r="D12" t="n">
-        <v>0.966816604067314</v>
+        <v>0.9997238235956329</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9979467580902408</v>
+        <v>0.9998698864093039</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9977196572024447</v>
+        <v>0.9998325018401061</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003039066897905543</v>
+        <v>0.0001170069679541256</v>
       </c>
       <c r="H12" t="n">
-        <v>0.176803221221785</v>
+        <v>0.1768783529629524</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0006768578391807073</v>
+        <v>9.731732726486265e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001693441711440518</v>
+        <v>8.617116560530644e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001185149775310613</v>
+        <v>9.174424643508455e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01836067509808225</v>
+        <v>0.006506960232386406</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05512773256633673</v>
+        <v>0.01081697591538992</v>
       </c>
       <c r="N12" t="n">
-        <v>1.004550532724663</v>
+        <v>1.000175199840798</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05747463427182411</v>
+        <v>0.01127747697433509</v>
       </c>
       <c r="P12" t="n">
-        <v>113.5924095043172</v>
+        <v>120.1065541395528</v>
       </c>
       <c r="Q12" t="n">
-        <v>175.7550765725955</v>
+        <v>182.269221207831</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_13</t>
+          <t>model_14_3_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9944157721527102</v>
+        <v>0.9998203061043774</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7019369986467384</v>
+        <v>0.7015329051649598</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9694187404034171</v>
+        <v>0.9997368831653743</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9979576189704921</v>
+        <v>0.999879905308688</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9977793453043234</v>
+        <v>0.9998427596974776</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003315038876233843</v>
+        <v>0.0001066740588136825</v>
       </c>
       <c r="H13" t="n">
-        <v>0.17694307325453</v>
+        <v>0.1771829606012433</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006237808008546344</v>
+        <v>9.271547713442149e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001684484039403388</v>
+        <v>7.953588459134165e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001154128412818054</v>
+        <v>8.612568086288157e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01905132528104155</v>
+        <v>0.006243058399327476</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05757637428871189</v>
+        <v>0.01032831345446499</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00496375808648</v>
+        <v>1.00015972790722</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06002751974170792</v>
+        <v>0.01076801114077784</v>
       </c>
       <c r="P13" t="n">
-        <v>113.4185718560848</v>
+        <v>120.2914651037231</v>
       </c>
       <c r="Q13" t="n">
-        <v>175.581238924363</v>
+        <v>182.4541321720014</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9938922114467452</v>
+        <v>0.9998356338221799</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7016647615208786</v>
+        <v>0.7010409588879232</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9719434489787515</v>
+        <v>0.9997461998904427</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9979387227543128</v>
+        <v>0.9998881106835776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9978138874174995</v>
+        <v>0.9998507172227916</v>
       </c>
       <c r="G14" t="n">
-        <v>0.003625847127939469</v>
+        <v>9.757486340322379e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1771046849724719</v>
+        <v>0.1774750011622649</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0005722830941603498</v>
+        <v>8.943250737966844e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001700068973898616</v>
+        <v>7.410165812281785e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001136176034029483</v>
+        <v>8.176708275124315e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01977962283550513</v>
+        <v>0.005992214356687322</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0602150074976286</v>
+        <v>0.009877998957441927</v>
       </c>
       <c r="N14" t="n">
-        <v>1.005429145380671</v>
+        <v>1.000146103269173</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06277848502905196</v>
+        <v>0.01029852582333699</v>
       </c>
       <c r="P14" t="n">
-        <v>113.2393346550216</v>
+        <v>120.4697812896286</v>
       </c>
       <c r="Q14" t="n">
-        <v>175.4020017232998</v>
+        <v>182.6324483579068</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_11</t>
+          <t>model_14_3_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9933034132912113</v>
+        <v>0.9998490936909505</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7013511649553341</v>
+        <v>0.7005695800134952</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9743794372613125</v>
+        <v>0.9997522053060169</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9978856306973234</v>
+        <v>0.9998946674522676</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9978195630935062</v>
+        <v>0.9998566129293883</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003975383147820358</v>
+        <v>8.95845038648767e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1772908494404454</v>
+        <v>0.1777548320246324</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0005225950583562837</v>
+        <v>8.731635631259709e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001743857435172824</v>
+        <v>6.975926469879132e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001133226246764554</v>
+        <v>7.853781050569421e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02054944414259087</v>
+        <v>0.005753879928661926</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06305063955123975</v>
+        <v>0.009464909078531959</v>
       </c>
       <c r="N15" t="n">
-        <v>1.005952521518923</v>
+        <v>1.000134138941377</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0657348358097529</v>
+        <v>0.009867849853067894</v>
       </c>
       <c r="P15" t="n">
-        <v>113.0552682922645</v>
+        <v>120.6406564017545</v>
       </c>
       <c r="Q15" t="n">
-        <v>175.2179353605427</v>
+        <v>182.8033234700328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_10</t>
+          <t>model_14_3_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9926419734688405</v>
+        <v>0.9998608681592406</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7009905024261258</v>
+        <v>0.7001183369211592</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9767101738357326</v>
+        <v>0.9997552583281796</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9977931997343328</v>
+        <v>0.9998997558904252</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9977919593845639</v>
+        <v>0.99986067125601</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00436804239909219</v>
+        <v>8.259467085734259e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1775049542975934</v>
+        <v>0.1780227094169297</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0004750538927485935</v>
+        <v>8.624055131171888e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001820091242505937</v>
+        <v>6.638931199200939e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001147572567627265</v>
+        <v>7.631493165186414e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02139816074240494</v>
+        <v>0.005534010170352589</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06609116733037926</v>
+        <v>0.009088161027256427</v>
       </c>
       <c r="N16" t="n">
-        <v>1.006540468027697</v>
+        <v>1.000123672747342</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06890480515121056</v>
+        <v>0.009475062857273583</v>
       </c>
       <c r="P16" t="n">
-        <v>112.8668806676695</v>
+        <v>120.8031307939685</v>
       </c>
       <c r="Q16" t="n">
-        <v>175.0295477359478</v>
+        <v>182.9657978622468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_9</t>
+          <t>model_14_3_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9918998474839699</v>
+        <v>0.9998711322036909</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7005768008728834</v>
+        <v>0.6996870746613122</v>
       </c>
       <c r="D17" t="n">
-        <v>0.978919471958086</v>
+        <v>0.9997557163741337</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9976558131013593</v>
+        <v>0.9999035277582825</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9977263019541897</v>
+        <v>0.9998630989199246</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004808600441884759</v>
+        <v>7.650149068798508e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1777505454105747</v>
+        <v>0.1782787253239345</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0004299897662126704</v>
+        <v>8.607914792126072e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001933402905279717</v>
+        <v>6.389129277637214e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001181696335746194</v>
+        <v>7.498522034881642e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02228918396845823</v>
+        <v>0.005342593509629448</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06934407286772792</v>
+        <v>0.008746513058812928</v>
       </c>
       <c r="N17" t="n">
-        <v>1.007200135569805</v>
+        <v>1.000114549152275</v>
       </c>
       <c r="O17" t="n">
-        <v>0.07229619361172691</v>
+        <v>0.009118870227504652</v>
       </c>
       <c r="P17" t="n">
-        <v>112.6746984112542</v>
+        <v>120.9564006624084</v>
       </c>
       <c r="Q17" t="n">
-        <v>174.8373654795325</v>
+        <v>183.1190677306866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_8</t>
+          <t>model_14_3_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9910680304330605</v>
+        <v>0.9998800415607744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7001028668575642</v>
+        <v>0.6992749588779277</v>
       </c>
       <c r="D18" t="n">
-        <v>0.980987115449905</v>
+        <v>0.9997539036864146</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9974671394473894</v>
+        <v>0.999906139350757</v>
       </c>
       <c r="F18" t="n">
-        <v>0.99761717039599</v>
+        <v>0.9998640947087429</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005302402975930186</v>
+        <v>7.121251145907853e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1780318931149517</v>
+        <v>0.1785233750554265</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000387815037956781</v>
+        <v>8.671789156917342e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002089014299126665</v>
+        <v>6.216169661036842e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001238414668541723</v>
+        <v>7.443979408977092e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02322450901150916</v>
+        <v>0.005161050129872991</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07281760072901459</v>
+        <v>0.008438750586377022</v>
       </c>
       <c r="N18" t="n">
-        <v>1.007939528503946</v>
+        <v>1.000106629723756</v>
       </c>
       <c r="O18" t="n">
-        <v>0.07591759674526248</v>
+        <v>0.008798005669461005</v>
       </c>
       <c r="P18" t="n">
-        <v>112.4791903389801</v>
+        <v>121.0996840644878</v>
       </c>
       <c r="Q18" t="n">
-        <v>174.6418574072584</v>
+        <v>183.2623511327661</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_7</t>
+          <t>model_14_3_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9901365401444843</v>
+        <v>0.9998877428694435</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6995610712482573</v>
+        <v>0.698881532665266</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9828894514784963</v>
+        <v>0.9997501343795188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9972200551133175</v>
+        <v>0.9999077156423163</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9974584481971707</v>
+        <v>0.999863833855317</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005855375849514281</v>
+        <v>6.664068195392e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1783535263929879</v>
+        <v>0.1787569298503899</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0003490121662941012</v>
+        <v>8.804609653869524e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.002292800767526803</v>
+        <v>6.111775584857759e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001320906466910452</v>
+        <v>7.458267208323986e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02420589062416222</v>
+        <v>0.004988873861396166</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0765204276616008</v>
+        <v>0.008163374422009565</v>
       </c>
       <c r="N19" t="n">
-        <v>1.00876751987157</v>
+        <v>1.00009978411605</v>
       </c>
       <c r="O19" t="n">
-        <v>0.07977806068627734</v>
+        <v>0.008510906171669178</v>
       </c>
       <c r="P19" t="n">
-        <v>112.2807901821565</v>
+        <v>121.2323906535118</v>
       </c>
       <c r="Q19" t="n">
-        <v>174.4434572504347</v>
+        <v>183.39505772179</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_6</t>
+          <t>model_14_3_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9890942392620518</v>
+        <v>0.9998943611568701</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6989426020521607</v>
+        <v>0.6985062203933579</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9845966736183686</v>
+        <v>0.999744647688488</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9969065415141307</v>
+        <v>0.9999083832944619</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9972431879995464</v>
+        <v>0.9998624739733644</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006474130678379962</v>
+        <v>6.271178064229114e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.178720676424269</v>
+        <v>0.1789797314276405</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000314189127358018</v>
+        <v>8.997946267060571e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002551375757372458</v>
+        <v>6.067558556261299e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001432782442365238</v>
+        <v>7.532752411660936e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02523511969875913</v>
+        <v>0.004825562962153598</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08046198281412137</v>
+        <v>0.007919077006968119</v>
       </c>
       <c r="N20" t="n">
-        <v>1.009694009544843</v>
+        <v>1.000093901193893</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08388741600178468</v>
+        <v>0.008256208509904054</v>
       </c>
       <c r="P20" t="n">
-        <v>112.0798818771505</v>
+        <v>121.3539224778851</v>
       </c>
       <c r="Q20" t="n">
-        <v>174.2425489454287</v>
+        <v>183.5165895461634</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_5</t>
+          <t>model_14_3_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9879289141857892</v>
+        <v>0.9999000200709698</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6982369728959056</v>
+        <v>0.6981482596515785</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9860748152187858</v>
+        <v>0.9997377073031456</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9965177018737932</v>
+        <v>0.9999082670226972</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9969636616237787</v>
+        <v>0.9998601711957349</v>
       </c>
       <c r="G21" t="n">
-        <v>0.007165917983071566</v>
+        <v>5.935240478038518e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1791395683730145</v>
+        <v>0.1791922323870597</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0002840387554162478</v>
+        <v>9.24250725816647e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002872077016624623</v>
+        <v>6.075258961292847e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00157805911821835</v>
+        <v>7.658883109729659e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0263142839164303</v>
+        <v>0.004670471167260585</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08465174530434423</v>
+        <v>0.007704051192741724</v>
       </c>
       <c r="N21" t="n">
-        <v>1.010729854057076</v>
+        <v>1.000088871048027</v>
       </c>
       <c r="O21" t="n">
-        <v>0.08825554535522034</v>
+        <v>0.008032028601601243</v>
       </c>
       <c r="P21" t="n">
-        <v>111.8768382109043</v>
+        <v>121.4640358382092</v>
       </c>
       <c r="Q21" t="n">
-        <v>174.0395052791825</v>
+        <v>183.6267029064874</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_4</t>
+          <t>model_14_3_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9866269704846797</v>
+        <v>0.999904817653206</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6974330528600086</v>
+        <v>0.6978072297536424</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9872793397803851</v>
+        <v>0.9997295362229831</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9960435837979844</v>
+        <v>0.9999074537852929</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9966111031657529</v>
+        <v>0.9998570516895907</v>
       </c>
       <c r="G22" t="n">
-        <v>0.007938808005089589</v>
+        <v>5.650435272017436e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1796168100338603</v>
+        <v>0.179394682466199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0002594694830711858</v>
+        <v>9.530434709500135e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.003263112930077517</v>
+        <v>6.129117758575169e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001761292348661236</v>
+        <v>7.829748712448876e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02744540453046261</v>
+        <v>0.004523444035297194</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08909998880521584</v>
+        <v>0.007516937722249291</v>
       </c>
       <c r="N22" t="n">
-        <v>1.011887137346951</v>
+        <v>1.000084606530484</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09289315979105751</v>
+        <v>0.007836949323291665</v>
       </c>
       <c r="P22" t="n">
-        <v>111.6719842805932</v>
+        <v>121.5623857669683</v>
       </c>
       <c r="Q22" t="n">
-        <v>173.8346513488714</v>
+        <v>183.7250528352465</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_3</t>
+          <t>model_14_3_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9851732085686373</v>
+        <v>0.9999088523391643</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6965174292743491</v>
+        <v>0.6974823542775159</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9881563853403716</v>
+        <v>0.9997203181707551</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9954729300429638</v>
+        <v>0.999906044918969</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9961755464592305</v>
+        <v>0.9998532347830642</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008801823877697221</v>
+        <v>5.410918884604991e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1801603637471871</v>
+        <v>0.1795875425827175</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0002415799589308663</v>
+        <v>9.855254712668982e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.003733768076433597</v>
+        <v>6.222423655878164e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001987661793388322</v>
+        <v>8.038813225878815e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0286303668822429</v>
+        <v>0.004383951652035112</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09381803599360423</v>
+        <v>0.007355894836527362</v>
       </c>
       <c r="N23" t="n">
-        <v>1.013179370161211</v>
+        <v>1.000081020142965</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0978120640159597</v>
+        <v>0.007669050508519823</v>
       </c>
       <c r="P23" t="n">
-        <v>111.4655926402878</v>
+        <v>121.6490130745091</v>
       </c>
       <c r="Q23" t="n">
-        <v>173.628259708566</v>
+        <v>183.8116801427874</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_2</t>
+          <t>model_14_3_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9835508447744723</v>
+        <v>0.9999122137800623</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6954755554995518</v>
+        <v>0.6971728277779358</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9886369025730721</v>
+        <v>0.9997102555068422</v>
       </c>
       <c r="E24" t="n">
-        <v>0.994793250500645</v>
+        <v>0.9999041259163709</v>
       </c>
       <c r="F24" t="n">
-        <v>0.995645623209675</v>
+        <v>0.9998488377865132</v>
       </c>
       <c r="G24" t="n">
-        <v>0.009764929108380348</v>
+        <v>5.211369232227138e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1807788650265104</v>
+        <v>0.1797712908837168</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0002317786156182513</v>
+        <v>0.0001020983661817712</v>
       </c>
       <c r="J24" t="n">
-        <v>0.004294343857545693</v>
+        <v>6.349514676726018e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00226307583237223</v>
+        <v>8.279651176222755e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02989522275195182</v>
+        <v>0.004251533207971132</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0988176558534979</v>
+        <v>0.00721898139090768</v>
       </c>
       <c r="N24" t="n">
-        <v>1.01462147131158</v>
+        <v>1.0000780321955</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1030245280439289</v>
+        <v>0.007526308374070207</v>
       </c>
       <c r="P24" t="n">
-        <v>111.2579159488926</v>
+        <v>121.7241656704883</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.4205830171709</v>
+        <v>183.8868327387666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_1</t>
+          <t>model_14_3_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9817412756331165</v>
+        <v>0.99991497835458</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6942903044381156</v>
+        <v>0.6968782627983805</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9886377089128177</v>
+        <v>0.9996995026249228</v>
       </c>
       <c r="E25" t="n">
-        <v>0.99399024552185</v>
+        <v>0.9999017780637467</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9950085118539709</v>
+        <v>0.9998439576313141</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01083916752000585</v>
+        <v>5.047252146517879e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1814824812567589</v>
+        <v>0.1799461573801254</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0002317621683149388</v>
+        <v>0.0001058873999740746</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004956634121114918</v>
+        <v>6.505007424420376e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002594198144714929</v>
+        <v>8.546953313463807e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03132383556961514</v>
+        <v>0.004125849530472894</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1041113227271935</v>
+        <v>0.007104401555738442</v>
       </c>
       <c r="N25" t="n">
-        <v>1.016229977215008</v>
+        <v>1.000075574795929</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1085435572758389</v>
+        <v>0.007406850638104858</v>
       </c>
       <c r="P25" t="n">
-        <v>111.0491781659342</v>
+        <v>121.788162998355</v>
       </c>
       <c r="Q25" t="n">
-        <v>173.2118452342125</v>
+        <v>183.9508300666332</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_14_3_0</t>
+          <t>model_14_3_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9797237510213096</v>
+        <v>0.9999172154406768</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6929428337080852</v>
+        <v>0.69659791104901</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9880515187798548</v>
+        <v>0.999688187986713</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9930484147873695</v>
+        <v>0.9998990599120035</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9942496988414915</v>
+        <v>0.999838675866723</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01203685728209974</v>
+        <v>4.914449052102696e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1822823980898096</v>
+        <v>0.1801125862891167</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0002437189730841428</v>
+        <v>0.0001098743819614668</v>
       </c>
       <c r="J26" t="n">
-        <v>0.005733422985254656</v>
+        <v>6.685024210327588e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002988571776699901</v>
+        <v>8.836252916849587e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0328232667599471</v>
+        <v>0.004006541186239865</v>
       </c>
       <c r="M26" t="n">
-        <v>0.109712612228949</v>
+        <v>0.007010313154276845</v>
       </c>
       <c r="N26" t="n">
-        <v>1.018023332425503</v>
+        <v>1.000073586274954</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1143833052679518</v>
+        <v>0.007308756698603198</v>
       </c>
       <c r="P26" t="n">
-        <v>110.8395637925107</v>
+        <v>121.8414916257041</v>
       </c>
       <c r="Q26" t="n">
-        <v>173.0022308607889</v>
+        <v>184.0041586939824</v>
       </c>
     </row>
   </sheetData>
